--- a/12602516.xlsx
+++ b/12602516.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Himanshu Gupta\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Himanshu Gupta\Desktop\Daily track\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{79C15563-114D-45D3-AF31-32F74F6ECF88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC9EDCE4-99CF-4E2A-BE18-A797A9B4B13C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -209,6 +209,18 @@
   </si>
   <si>
     <t>August</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Good Day</t>
   </si>
 </sst>
 </file>
@@ -1080,26 +1092,50 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
+      <c r="A8" s="13">
+        <v>46259</v>
+      </c>
+      <c r="B8" s="14">
+        <v>420</v>
+      </c>
+      <c r="C8" s="14">
+        <v>60</v>
+      </c>
+      <c r="D8" s="14">
+        <v>120</v>
+      </c>
+      <c r="E8" s="14">
+        <v>120</v>
+      </c>
+      <c r="F8" s="14">
+        <v>250</v>
+      </c>
+      <c r="G8" s="14">
+        <v>5</v>
+      </c>
+      <c r="H8" s="14">
+        <v>90</v>
+      </c>
+      <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="17"/>
+        <v>380</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="13"/>

--- a/12602516.xlsx
+++ b/12602516.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Himanshu Gupta\Desktop\Daily track\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC9EDCE4-99CF-4E2A-BE18-A797A9B4B13C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72F1AE5F-B546-4DC2-89B0-3607B2074E17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -221,6 +221,15 @@
   </si>
   <si>
     <t>Good Day</t>
+  </si>
+  <si>
+    <t>Neutral</t>
+  </si>
+  <si>
+    <t>Hectic Day</t>
+  </si>
+  <si>
+    <t>Project working day</t>
   </si>
 </sst>
 </file>
@@ -1093,7 +1102,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="13">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B8" s="14">
         <v>420</v>
@@ -1138,70 +1147,140 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+      <c r="A9" s="13">
+        <v>46261</v>
+      </c>
+      <c r="B9" s="14">
+        <v>400</v>
+      </c>
+      <c r="C9" s="14">
+        <v>60</v>
+      </c>
+      <c r="D9" s="14">
+        <v>150</v>
+      </c>
+      <c r="E9" s="14">
+        <v>120</v>
+      </c>
+      <c r="F9" s="14">
+        <v>250</v>
+      </c>
+      <c r="G9" s="14">
+        <v>5</v>
+      </c>
+      <c r="H9" s="14">
+        <v>60</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="17"/>
+        <v>400</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+      <c r="A10" s="13">
+        <v>46262</v>
+      </c>
+      <c r="B10" s="14">
+        <v>360</v>
+      </c>
+      <c r="C10" s="14">
+        <v>90</v>
+      </c>
+      <c r="D10" s="14">
+        <v>120</v>
+      </c>
+      <c r="E10" s="14">
+        <v>100</v>
+      </c>
+      <c r="F10" s="14">
+        <v>200</v>
+      </c>
+      <c r="G10" s="14">
+        <v>4</v>
+      </c>
+      <c r="H10" s="14">
+        <v>120</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="17"/>
+        <v>450</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
+      <c r="A11" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B11" s="14">
+        <v>480</v>
+      </c>
+      <c r="C11" s="14">
+        <v>90</v>
+      </c>
+      <c r="D11" s="14">
+        <v>300</v>
+      </c>
+      <c r="E11" s="14">
+        <v>240</v>
+      </c>
+      <c r="F11" s="14">
+        <v>0</v>
+      </c>
       <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="H11" s="14">
+        <v>180</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>1290</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
+        <v>150</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="13"/>

--- a/12602516.xlsx
+++ b/12602516.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Himanshu Gupta\Desktop\Daily track\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72F1AE5F-B546-4DC2-89B0-3607B2074E17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0DE3267-E8C9-4028-8510-AACDCEF84F6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="67">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -230,6 +230,12 @@
   </si>
   <si>
     <t>Project working day</t>
+  </si>
+  <si>
+    <t>Working day</t>
+  </si>
+  <si>
+    <t>Tired day</t>
   </si>
 </sst>
 </file>
@@ -1283,48 +1289,94 @@
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
+      <c r="A12" s="13">
+        <v>46264</v>
+      </c>
+      <c r="B12" s="14">
+        <v>420</v>
+      </c>
+      <c r="C12" s="14">
+        <v>0</v>
+      </c>
+      <c r="D12" s="14">
+        <v>240</v>
+      </c>
+      <c r="E12" s="14">
+        <v>200</v>
+      </c>
+      <c r="F12" s="14">
+        <v>0</v>
+      </c>
       <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="H12" s="14">
+        <v>120</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>980</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
+        <v>460</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="A13" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B13" s="14">
+        <v>420</v>
+      </c>
+      <c r="C13" s="14">
+        <v>60</v>
+      </c>
+      <c r="D13" s="14">
+        <v>120</v>
+      </c>
+      <c r="E13" s="14">
+        <v>100</v>
+      </c>
+      <c r="F13" s="14">
+        <v>100</v>
+      </c>
+      <c r="G13" s="14">
+        <v>2</v>
+      </c>
+      <c r="H13" s="14">
+        <v>100</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>900</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+        <v>540</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>

--- a/12602516.xlsx
+++ b/12602516.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Himanshu Gupta\Desktop\Daily track\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0DE3267-E8C9-4028-8510-AACDCEF84F6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CE6928B-F09C-4B0B-A374-0818AEF294DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -236,6 +236,12 @@
   </si>
   <si>
     <t>Tired day</t>
+  </si>
+  <si>
+    <t>It was busy day</t>
+  </si>
+  <si>
+    <t>Low</t>
   </si>
 </sst>
 </file>
@@ -1379,48 +1385,96 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="A14" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B14" s="14">
+        <v>400</v>
+      </c>
+      <c r="C14" s="14">
+        <v>80</v>
+      </c>
+      <c r="D14" s="14">
+        <v>140</v>
+      </c>
+      <c r="E14" s="14">
+        <v>90</v>
+      </c>
+      <c r="F14" s="14">
+        <v>250</v>
+      </c>
+      <c r="G14" s="14">
+        <v>5</v>
+      </c>
+      <c r="H14" s="14">
+        <v>120</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+        <v>360</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="A15" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B15" s="14">
+        <v>420</v>
+      </c>
+      <c r="C15" s="14">
+        <v>90</v>
+      </c>
+      <c r="D15" s="14">
+        <v>100</v>
+      </c>
+      <c r="E15" s="14">
+        <v>50</v>
+      </c>
+      <c r="F15" s="14">
+        <v>250</v>
+      </c>
+      <c r="G15" s="14">
+        <v>5</v>
+      </c>
+      <c r="H15" s="14">
+        <v>180</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+        <v>350</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="13"/>

--- a/12602516.xlsx
+++ b/12602516.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Himanshu Gupta\Desktop\Daily track\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CE6928B-F09C-4B0B-A374-0818AEF294DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECCFA039-CF9A-40F5-89AD-A4C546D98BDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -242,6 +242,9 @@
   </si>
   <si>
     <t>Low</t>
+  </si>
+  <si>
+    <t>Preparing for CA</t>
   </si>
 </sst>
 </file>
@@ -1477,136 +1480,280 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="A16" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B16" s="14">
+        <v>400</v>
+      </c>
+      <c r="C16" s="14">
+        <v>90</v>
+      </c>
+      <c r="D16" s="14">
+        <v>120</v>
+      </c>
+      <c r="E16" s="14">
+        <v>90</v>
+      </c>
+      <c r="F16" s="14">
+        <v>200</v>
+      </c>
+      <c r="G16" s="14">
+        <v>4</v>
+      </c>
+      <c r="H16" s="14">
+        <v>100</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>1000</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+        <v>440</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="A17" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B17" s="14">
+        <v>430</v>
+      </c>
+      <c r="C17" s="14">
+        <v>90</v>
+      </c>
+      <c r="D17" s="14">
+        <v>140</v>
+      </c>
+      <c r="E17" s="14">
+        <v>60</v>
+      </c>
+      <c r="F17" s="14">
+        <v>200</v>
+      </c>
+      <c r="G17" s="14">
+        <v>4</v>
+      </c>
+      <c r="H17" s="14">
+        <v>120</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+        <v>400</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="A18" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B18" s="14">
+        <v>460</v>
+      </c>
+      <c r="C18" s="14">
+        <v>0</v>
+      </c>
+      <c r="D18" s="14">
+        <v>150</v>
+      </c>
+      <c r="E18" s="14">
+        <v>50</v>
+      </c>
+      <c r="F18" s="14">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14">
+        <v>0</v>
+      </c>
+      <c r="H18" s="14">
+        <v>70</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>730</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+        <v>710</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="13">
+        <v>46271</v>
+      </c>
+      <c r="B19" s="14">
+        <v>450</v>
+      </c>
+      <c r="C19" s="14">
+        <v>0</v>
+      </c>
+      <c r="D19" s="14">
+        <v>190</v>
+      </c>
+      <c r="E19" s="14">
+        <v>30</v>
+      </c>
+      <c r="F19" s="14">
+        <v>0</v>
+      </c>
+      <c r="G19" s="14">
+        <v>0</v>
+      </c>
+      <c r="H19" s="14">
+        <v>100</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>770</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>670</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="A20" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B20" s="14">
+        <v>250</v>
+      </c>
+      <c r="C20" s="14">
+        <v>0</v>
+      </c>
+      <c r="D20" s="14">
+        <v>120</v>
+      </c>
+      <c r="E20" s="14">
+        <v>50</v>
+      </c>
+      <c r="F20" s="14">
+        <v>300</v>
+      </c>
+      <c r="G20" s="14">
+        <v>6</v>
+      </c>
+      <c r="H20" s="14">
+        <v>120</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>840</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+        <v>600</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="A21" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B21" s="14">
+        <v>360</v>
+      </c>
+      <c r="C21" s="14">
+        <v>0</v>
+      </c>
+      <c r="D21" s="14">
+        <v>100</v>
+      </c>
+      <c r="E21" s="14">
+        <v>130</v>
+      </c>
+      <c r="F21" s="14">
+        <v>200</v>
+      </c>
+      <c r="G21" s="14">
+        <v>4</v>
+      </c>
+      <c r="H21" s="14">
+        <v>100</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>890</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>550</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="13"/>
